--- a/data/raw/inventory/Week 24/White_Mulberry/Inventory Snapshot.xlsx
+++ b/data/raw/inventory/Week 24/White_Mulberry/Inventory Snapshot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 24\White_Mulberry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A16D1F8-7575-46A2-83E9-0D40E7F1EA0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89954FD-4069-4718-862D-D36987A021E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$71</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="99">
   <si>
     <t>SKU</t>
   </si>
@@ -315,12 +315,6 @@
     <t>B2B - AMPM</t>
   </si>
   <si>
-    <t>Pipeline</t>
-  </si>
-  <si>
-    <t>In-Transit Inventory</t>
-  </si>
-  <si>
     <t>Open Order</t>
   </si>
   <si>
@@ -334,17 +328,19 @@
   </si>
   <si>
     <t>1P</t>
+  </si>
+  <si>
+    <t>WM1ML</t>
+  </si>
+  <si>
+    <t>TVCT1ML</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,12 +392,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1F2937"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -447,13 +437,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -479,41 +468,16 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="Comma" xfId="3" builtinId="3"/>
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{697FC575-8A7C-4715-A8F0-2950C62D8576}"/>
     <cellStyle name="Normal 6" xfId="1" xr:uid="{E5F241CE-C0FC-4730-81C9-F1901EB82A3C}"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="9">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -934,7 +898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -2371,160 +2335,151 @@
       </c>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I62" s="9">
+        <v>5</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K62" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I63" s="9">
+        <v>4</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K63" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I64" s="9">
+        <v>3</v>
+      </c>
+      <c r="J64" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K64" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I65" s="9">
+        <v>2</v>
+      </c>
+      <c r="J65" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K65" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B66" t="s">
+        <v>63</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I66" s="1">
+        <v>42</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B67" t="s">
+        <v>50</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I67" s="1">
+        <v>22</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B68" t="s">
+        <v>47</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I68" s="1">
         <v>15</v>
       </c>
-      <c r="B62" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="I62" s="10">
-        <v>500</v>
-      </c>
-      <c r="J62" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="K62" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="L62" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="I63" s="10">
-        <v>1000</v>
-      </c>
-      <c r="J63" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="K63" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="L63" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="I64" s="10">
-        <v>1000</v>
-      </c>
-      <c r="J64" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="K64" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="L64" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B65" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I65" s="11">
-        <v>5</v>
-      </c>
-      <c r="J65" s="7" t="s">
+      <c r="J68" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="K65" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="L65" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I66" s="11">
-        <v>4</v>
-      </c>
-      <c r="J66" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="K66" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="L66" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I67" s="11">
-        <v>3</v>
-      </c>
-      <c r="J67" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="K67" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="L67" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B68" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I68" s="11">
-        <v>2</v>
-      </c>
-      <c r="J68" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="K68" s="8" t="s">
+      <c r="K68" s="1" t="s">
         <v>96</v>
       </c>
       <c r="L68" s="1" t="s">
@@ -2533,19 +2488,19 @@
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>85</v>
       </c>
       <c r="I69" s="1">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L69" s="1" t="s">
         <v>82</v>
@@ -2553,19 +2508,19 @@
     </row>
     <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>85</v>
       </c>
       <c r="I70" s="1">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L70" s="1" t="s">
         <v>82</v>
@@ -2573,113 +2528,86 @@
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>85</v>
       </c>
       <c r="I71" s="1">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="J71" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K71" s="1" t="s">
+      <c r="I72" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="L71" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B72" t="s">
-        <v>62</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I72" s="1">
-        <v>19</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="L72" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" t="s">
-        <v>48</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="I73" s="1">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="L73" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" t="s">
-        <v>46</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I74" s="1">
-        <v>107</v>
-      </c>
-      <c r="J74" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="L74" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L74" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A35:A56">
+    <cfRule type="duplicateValues" dxfId="8" priority="2168"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A62:A65">
+    <cfRule type="duplicateValues" dxfId="7" priority="2161"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="10" priority="1894"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1894"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="9" priority="2105"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="2106" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2105"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2106" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="7" priority="1892"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="1893" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1892"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1893" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="5" priority="1890"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1891" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A65:A68">
-    <cfRule type="duplicateValues" dxfId="3" priority="2161"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A63:A64">
-    <cfRule type="duplicateValues" dxfId="2" priority="2164"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A62">
-    <cfRule type="duplicateValues" dxfId="1" priority="2165"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A56">
-    <cfRule type="duplicateValues" dxfId="0" priority="2168"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1890"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1891" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
